--- a/Capitulo000_ClaseOnline/Cohorte04/Clase24_26082025Borrador/EsquemaDiagramaCompleto.xlsx
+++ b/Capitulo000_ClaseOnline/Cohorte04/Clase24_26082025Borrador/EsquemaDiagramaCompleto.xlsx
@@ -136,15 +136,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>596346</xdr:colOff>
+      <xdr:colOff>612911</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>137908</xdr:rowOff>
+      <xdr:rowOff>113060</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>167721</xdr:colOff>
+      <xdr:colOff>184286</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>52183</xdr:rowOff>
+      <xdr:rowOff>27335</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -159,7 +159,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6725476" y="1280908"/>
+          <a:off x="6742041" y="1256060"/>
           <a:ext cx="2635941" cy="676275"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -289,16 +289,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>476249</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>85724</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>335444</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>118028</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>557832</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>118028</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -313,8 +313,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12058649" y="2428875"/>
-          <a:ext cx="2047875" cy="2095500"/>
+          <a:off x="13819531" y="4690028"/>
+          <a:ext cx="2061127" cy="2095500"/>
         </a:xfrm>
         <a:prstGeom prst="can">
           <a:avLst/>
@@ -363,8 +363,8 @@
       <xdr:rowOff>95249</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>314325</xdr:colOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>488674</xdr:colOff>
       <xdr:row>20</xdr:row>
       <xdr:rowOff>123824</xdr:rowOff>
     </xdr:to>
@@ -381,8 +381,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9496425" y="3143249"/>
-          <a:ext cx="2400300" cy="790575"/>
+          <a:off x="9546121" y="3143249"/>
+          <a:ext cx="3200814" cy="790575"/>
         </a:xfrm>
         <a:prstGeom prst="leftRightArrow">
           <a:avLst/>
@@ -1307,16 +1307,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>561974</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>257175</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>545408</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>138319</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>240609</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>90694</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1325,8 +1325,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12144374" y="3981450"/>
-          <a:ext cx="2133601" cy="523875"/>
+          <a:off x="13416582" y="5091319"/>
+          <a:ext cx="2146853" cy="523875"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
           <a:avLst/>
@@ -1593,6 +1593,137 @@
             <a:t> =&gt; ELIMINAR DATOS</a:t>
           </a:r>
           <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>107673</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>603388</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>107673</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="26" name="Cilindro 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15090913" y="488673"/>
+          <a:ext cx="2061127" cy="2095500"/>
+        </a:xfrm>
+        <a:prstGeom prst="can">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent4">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent4"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="2000"/>
+            <a:t>MONGO</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="2000" baseline="0"/>
+            <a:t> DB</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="2000"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>107674</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>57978</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>446433</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>115128</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="27" name="Nube 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11753022" y="248478"/>
+          <a:ext cx="2177498" cy="1962150"/>
+        </a:xfrm>
+        <a:prstGeom prst="cloud">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="2000"/>
+            <a:t>INTERNET</a:t>
+          </a:r>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
